--- a/docs/sample-report.xlsx
+++ b/docs/sample-report.xlsx
@@ -108,16 +108,15 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -130,14 +129,14 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">رحلة سيدي إبراهيم الدسوقي — الأربعاء، 28 أكتوبر 2026 — التحرك 6:00 صباحًا من مفارق الـ100 بالشروق</t>
+          <t xml:space="preserve">رحلة سيدي إبراهيم الدسوقي — الأربعاء، 28 أكتوبر 2026 — التحرك 7:30 صباحًا من الشروق</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 من 50 مقعدًا محجوزًا — عدد الحجوزات: 10</t>
+          <t xml:space="preserve">30 من 50 مقعدًا محجوزًا — عدد الحجوزات: 10</t>
         </is>
       </c>
     </row>
@@ -149,50 +148,45 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">رقم الحجز</t>
+          <t xml:space="preserve">الاسم الكامل</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">الاسم الكامل</t>
+          <t xml:space="preserve">عدد المقاعد</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">عدد المقاعد</t>
+          <t xml:space="preserve">نقطة التجمع</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">نقطة التجمع</t>
+          <t xml:space="preserve">رقم الهاتف</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">رقم الهاتف</t>
+          <t xml:space="preserve">المبلغ (جنيه)</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">المبلغ (جنيه)</t>
+          <t xml:space="preserve">الدفع</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">الدفع</t>
+          <t xml:space="preserve">ملاحظات</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ملاحظات</t>
+          <t xml:space="preserve">وقت التسجيل</t>
         </is>
       </c>
       <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">وقت التسجيل</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">الحالة</t>
         </is>
@@ -204,42 +198,37 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSQ-UZAN-8YGU</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">محمد عبد الرحمن</t>
         </is>
       </c>
-      <c r="D6" s="3">
+      <c r="C6" s="3">
         <v>3</v>
       </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المستقبل</t>
+        </is>
+      </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">مفارق الـ100 بالشروق</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">01001234567</t>
         </is>
       </c>
-      <c r="G6" s="3">
+      <c r="F6" s="3">
         <v>900</v>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">مدفوع</t>
         </is>
       </c>
-      <c r="I6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15 19:13</t>
+        </is>
+      </c>
       <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-13 08:14</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">مؤكد</t>
         </is>
@@ -251,46 +240,41 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSQ-PKM7-KPAB</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">أحمد السيد</t>
         </is>
       </c>
-      <c r="D7" s="3">
+      <c r="C7" s="3">
         <v>2</v>
       </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الشروق</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">صينية النهضة بالشروق</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">01112345678</t>
         </is>
       </c>
-      <c r="G7" s="3">
+      <c r="F7" s="3">
         <v>600</v>
       </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مدفوع</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدفوع</t>
+          <t xml:space="preserve">معي كرسي متحرك قابل للطي</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">معي كرسي متحرك قابل للطي</t>
+          <t xml:space="preserve">2026-10-15 22:13</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-13 11:14</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">مؤكد</t>
         </is>
@@ -302,38 +286,33 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSQ-EURE-9TCU</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">فاطمة إبراهيم</t>
         </is>
       </c>
-      <c r="D8" s="3">
+      <c r="C8" s="3">
         <v>4</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">المستقبل</t>
         </is>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3">
+      <c r="E8" s="3"/>
+      <c r="F8" s="3">
         <v>1200</v>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">لم يُدفع</t>
         </is>
       </c>
-      <c r="I8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16 01:13</t>
+        </is>
+      </c>
       <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-13 14:14</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">مؤكد</t>
         </is>
@@ -345,42 +324,37 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSQ-8RHD-9QEU</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">محمود فتحي</t>
         </is>
       </c>
-      <c r="D9" s="3">
+      <c r="C9" s="3">
         <v>1</v>
       </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الشروق</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">كارفور العبور</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">01223456789</t>
         </is>
       </c>
-      <c r="G9" s="3">
+      <c r="F9" s="3">
         <v>300</v>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">مدفوع</t>
         </is>
       </c>
-      <c r="I9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16 04:13</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-13 17:14</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">مؤكد</t>
         </is>
@@ -392,46 +366,41 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSQ-N7UK-GERB</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">حسن علي</t>
         </is>
       </c>
-      <c r="D10" s="3">
+      <c r="C10" s="3">
         <v>5</v>
       </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المستقبل</t>
+        </is>
+      </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">مفارق الـ100 بالشروق</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">01556789012</t>
         </is>
       </c>
-      <c r="G10" s="3">
+      <c r="F10" s="3">
         <v>1500</v>
       </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لم يُدفع</t>
+        </is>
+      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">لم يُدفع</t>
+          <t xml:space="preserve">عائلة</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">عائلة</t>
+          <t xml:space="preserve">2026-10-16 07:13</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-13 20:14</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">مؤكد</t>
         </is>
@@ -443,38 +412,33 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSQ-FT73-BMEG</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">سعاد محمد</t>
         </is>
       </c>
-      <c r="D11" s="3">
+      <c r="C11" s="3">
         <v>2</v>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">صينية النهضة بالشروق</t>
-        </is>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الشروق</t>
+        </is>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3">
         <v>600</v>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">مدفوع</t>
         </is>
       </c>
-      <c r="I11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16 10:13</t>
+        </is>
+      </c>
       <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-13 23:14</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">مؤكد</t>
         </is>
@@ -486,42 +450,37 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSQ-6BJM-Y5C8</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">خالد يوسف</t>
         </is>
       </c>
-      <c r="D12" s="3">
+      <c r="C12" s="3">
         <v>6</v>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">مفارق الـ100 بالشروق</t>
-        </is>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المستقبل</t>
+        </is>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3">
         <v>1800</v>
       </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لم يُدفع</t>
+        </is>
+      </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">لم يُدفع</t>
+          <t xml:space="preserve">مجموعة من المسجد</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">مجموعة من المسجد</t>
+          <t xml:space="preserve">2026-10-16 16:13</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-14 05:14</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">مؤكد</t>
         </is>
@@ -533,42 +492,37 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSQ-7KK8-4ZTA</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">منى حسين</t>
         </is>
       </c>
-      <c r="D13" s="3">
+      <c r="C13" s="3">
         <v>2</v>
       </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الشروق</t>
+        </is>
+      </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">كارفور العبور</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">01187654321</t>
         </is>
       </c>
-      <c r="G13" s="3">
+      <c r="F13" s="3">
         <v>600</v>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">مدفوع</t>
         </is>
       </c>
-      <c r="I13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16 19:13</t>
+        </is>
+      </c>
       <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-14 08:14</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">مؤكد</t>
         </is>
@@ -580,38 +534,33 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSQ-UHUB-GZB4</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">إبراهيم الدسوقي</t>
         </is>
       </c>
-      <c r="D14" s="3">
+      <c r="C14" s="3">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">صينية النهضة بالشروق</t>
-        </is>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الشروق</t>
+        </is>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">لم يُدفع</t>
         </is>
       </c>
-      <c r="I14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16 22:13</t>
+        </is>
+      </c>
       <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-14 11:14</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">مؤكد</t>
         </is>
@@ -623,38 +572,33 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSQ-QW2Y-7Q6E</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">عبد الحكيم طلعت</t>
-        </is>
-      </c>
-      <c r="D15" s="3">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">مفارق الـ100 بالشروق</t>
-        </is>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3">
-        <v>900</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">مدفوع</t>
-        </is>
-      </c>
-      <c r="I15" s="3"/>
+          <t xml:space="preserve">عبد الحكيم طلعت محمد</t>
+        </is>
+      </c>
+      <c r="C15" s="3">
+        <v>2</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الشروق</t>
+        </is>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3">
+        <v>600</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لم يُدفع</t>
+        </is>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17 11:13</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15 00:15</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">مؤكد</t>
         </is>
@@ -662,34 +606,33 @@
     </row>
     <row r="16">
       <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">الإجمالي</t>
         </is>
       </c>
-      <c r="D16" s="3">
-        <v>31</v>
-      </c>
+      <c r="C16" s="3">
+        <v>30</v>
+      </c>
+      <c r="D16" s="3"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3">
-        <v>9300</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">مدفوع 3900</t>
-        </is>
-      </c>
+      <c r="F16" s="3">
+        <v>9000</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مدفوع 3000</t>
+        </is>
+      </c>
+      <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -717,7 +660,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">رحلة سيدي إبراهيم الدسوقي — الأربعاء، 28 أكتوبر 2026 — التحرك 6:00 صباحًا من مفارق الـ100 بالشروق</t>
+          <t xml:space="preserve">رحلة سيدي إبراهيم الدسوقي — الأربعاء، 28 أكتوبر 2026 — التحرك 7:30 صباحًا من الشروق</t>
         </is>
       </c>
     </row>
@@ -753,7 +696,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6:00 صباحًا</t>
+          <t xml:space="preserve">7:30 صباحًا</t>
         </is>
       </c>
     </row>
@@ -765,7 +708,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">مفارق الـ100 بالشروق</t>
+          <t xml:space="preserve">الشروق</t>
         </is>
       </c>
     </row>
@@ -820,7 +763,7 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -830,7 +773,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -841,7 +784,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62%</t>
+          <t xml:space="preserve">60%</t>
         </is>
       </c>
     </row>
@@ -874,7 +817,7 @@
         </is>
       </c>
       <c r="B17" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -884,7 +827,7 @@
         </is>
       </c>
       <c r="B18" s="3">
-        <v>9300</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="19">
@@ -894,7 +837,7 @@
         </is>
       </c>
       <c r="B19" s="3">
-        <v>3900</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="20">
@@ -904,7 +847,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <v>5400</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="21">
@@ -925,7 +868,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15 00:15</t>
+          <t xml:space="preserve">2026-10-17 11:13</t>
         </is>
       </c>
     </row>
@@ -978,66 +921,40 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">مفارق الـ100 بالشروق</t>
+          <t xml:space="preserve">المستقبل</t>
         </is>
       </c>
       <c r="B4" s="3">
         <v>4</v>
       </c>
       <c r="C4" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">صينية النهضة بالشروق</t>
+          <t xml:space="preserve">الشروق</t>
         </is>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">المستقبل</t>
+          <t xml:space="preserve">الإجمالي</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">كارفور العبور</t>
-        </is>
-      </c>
-      <c r="B7" s="3">
-        <v>2</v>
-      </c>
-      <c r="C7" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الإجمالي</t>
-        </is>
-      </c>
-      <c r="B8" s="3">
-        <v>10</v>
-      </c>
-      <c r="C8" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1056,14 +973,13 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1076,40 +992,35 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">رقم الحجز</t>
+          <t xml:space="preserve">الاسم الكامل</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">الاسم الكامل</t>
+          <t xml:space="preserve">عدد المقاعد</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">عدد المقاعد</t>
+          <t xml:space="preserve">نقطة التجمع</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">نقطة التجمع</t>
+          <t xml:space="preserve">رقم الهاتف</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">رقم الهاتف</t>
+          <t xml:space="preserve">كان مدفوعًا</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">كان مدفوعًا</t>
+          <t xml:space="preserve">وقت التسجيل</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">وقت التسجيل</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">وقت الإلغاء</t>
         </is>
@@ -1118,46 +1029,41 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSQ-XX2W-2DC9</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">عبد الله مصطفى</t>
         </is>
       </c>
-      <c r="C4" s="3">
+      <c r="B4" s="3">
         <v>3</v>
       </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المستقبل</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">المستقبل</t>
+          <t xml:space="preserve">01098765432</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01098765432</t>
+          <t xml:space="preserve">لا</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">لا</t>
+          <t xml:space="preserve">2026-10-16 13:13</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14 02:14</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-14 19:14</t>
+          <t xml:space="preserve">2026-10-17 06:13</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
